--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="174">
   <si>
     <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
   </si>
@@ -265,6 +265,33 @@
     <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
   </si>
   <si>
+    <t>hightech</t>
+  </si>
+  <si>
+    <t>这个高科技的名字</t>
+  </si>
+  <si>
+    <t>高科技的效果</t>
+  </si>
+  <si>
+    <t>timeCostBase</t>
+  </si>
+  <si>
+    <t>升级高科技需要的基础时间</t>
+  </si>
+  <si>
+    <t>timeCostMutiple</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>通过第几关后解锁</t>
+  </si>
+  <si>
+    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
+  </si>
+  <si>
     <t>如上</t>
   </si>
   <si>
@@ -488,6 +515,45 @@
   </si>
   <si>
     <t>死亡时后退距离</t>
+  </si>
+  <si>
+    <t>hightechLimit</t>
+  </si>
+  <si>
+    <t>同时研发的高科技数量</t>
+  </si>
+  <si>
+    <t>这个神器的名字</t>
+  </si>
+  <si>
+    <t>神器的效果</t>
+  </si>
+  <si>
+    <t>升级神器需要的基础时间</t>
+  </si>
+  <si>
+    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
+  </si>
+  <si>
+    <t>可变参数，具体效果参看神器的效果des</t>
+  </si>
+  <si>
+    <t>超时空炼铁炉</t>
+  </si>
+  <si>
+    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，向上取整，点击获取，10秒后消失</t>
+  </si>
+  <si>
+    <t>正电子聚焦装置</t>
+  </si>
+  <si>
+    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）向上取整.</t>
+  </si>
+  <si>
+    <t>简并态装甲</t>
+  </si>
+  <si>
+    <t>armour当前值增加（1+para1*等级），向上取整。</t>
   </si>
 </sst>
 </file>
@@ -1103,8 +1169,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1429,7 +1498,7 @@
   <cols>
     <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
     <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="30.2222222222222" customWidth="1"/>
     <col min="4" max="4" width="10.1111111111111" customWidth="1"/>
     <col min="5" max="5" width="11.8888888888889" customWidth="1"/>
     <col min="7" max="7" width="17.5555555555556" customWidth="1"/>
@@ -1442,7 +1511,7 @@
       <c r="B1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D1" t="s">
@@ -1452,7 +1521,7 @@
         <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G1" t="s">
         <v>59</v>
@@ -1469,7 +1538,7 @@
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
@@ -1478,7 +1547,7 @@
         <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G2" t="s">
         <v>60</v>
@@ -1489,22 +1558,22 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="G3" t="s">
         <v>61</v>
@@ -1518,13 +1587,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D4">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -1533,7 +1602,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1544,13 +1613,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D5">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -1559,7 +1628,7 @@
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1570,13 +1639,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D6">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E6">
         <v>10</v>
@@ -1585,7 +1654,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1596,22 +1665,22 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="D7">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1622,13 +1691,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E8">
         <v>300</v>
@@ -1637,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1648,13 +1717,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E9">
         <v>300</v>
@@ -1663,7 +1732,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="H9">
         <v>2</v>

--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -2,17 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13380" activeTab="0" firstSheet="0"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="mon" sheetId="4" r:id="rId4" state="visible"/>
+    <sheet name="mon" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,162 +27,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="174">
-  <si>
-    <t>太空战舰是一个科幻飞行器不断攻击敌方飞行器的小游戏，横版，即时，有相关画面。玩家不需操作</t>
-  </si>
-  <si>
-    <t>战舰会自动使用武器，攻击敌方飞行器，武器有各种参数，在武器表里定义</t>
-  </si>
-  <si>
-    <t>在每个关卡，敌方飞行器每隔一段距离就会出现。全部击落后才能前进，战斗时无法移动。关卡最后出现一个敌方BOSS飞行器，击毁后通关</t>
-  </si>
-  <si>
-    <t>敌方飞行器有各种参数，在怪物表里配置。怪物群负责整理一整群怪物，而关卡表将配置怪物群，用来辨别哪些敌方飞行器将出现在关卡里及出现在关卡的什么位置</t>
-  </si>
-  <si>
-    <t>敌方飞行器被击毁后会掉落资源，鼠标划过可以拾取。如果一段时间没有拾取，则自动拾取，但会有损耗，损耗比例在config里配置</t>
-  </si>
-  <si>
-    <t>飞行器初始武器为激光，激光会发射一道光束，攻击一个目标。</t>
-  </si>
-  <si>
-    <t>第二个武器为导弹，导弹在通关第一关后获得，导弹会同时发射3枚导弹，锁定3个敌人（若不足则只发射对应数量的导弹）</t>
-  </si>
-  <si>
-    <t>玩家可以选择任何一个已经通关过的关卡重新通关，或者无限循环该关卡。如果选择循环，则击败BOSS后就从这关开始重新前进</t>
-  </si>
-  <si>
-    <t>具体配置如下，表格均从第四行开始是实际配置</t>
-  </si>
-  <si>
-    <t>表格名</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>列名</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>关卡的id</t>
-  </si>
-  <si>
-    <t>length</t>
-  </si>
-  <si>
-    <t>关卡长度</t>
-  </si>
-  <si>
-    <t>monGroup</t>
-  </si>
-  <si>
-    <t>怪物群id</t>
-  </si>
-  <si>
-    <t>格式为{id|比例，id|比例....}，id为monGroup表的id，比例表示在关卡长度的%多少处出现</t>
-  </si>
-  <si>
-    <t>atkRatio</t>
-  </si>
-  <si>
-    <t>攻击倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的器伤害*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>所有倍率，在关卡中由上一关的倍率线性成长到本关倍率。如第一关倍率是1，第二关倍率是10，则10%的长度时是2..以此类推</t>
-  </si>
-  <si>
-    <t>lifeRatio</t>
-  </si>
-  <si>
-    <t>生命倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器的生命*这个值（向上取整，没有小数）</t>
-  </si>
-  <si>
-    <t>resRatio</t>
-  </si>
-  <si>
-    <t>资源倍率</t>
-  </si>
-  <si>
-    <t>敌方飞行器摧毁时获得的资源乘该值</t>
+    <t>des</t>
   </si>
   <si>
     <t>equipment</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>武器名</t>
-  </si>
-  <si>
-    <t>des</t>
-  </si>
-  <si>
-    <t>武器说明</t>
-  </si>
-  <si>
-    <t>武器等级</t>
-  </si>
-  <si>
-    <t>dmg</t>
-  </si>
-  <si>
-    <t>武器命中时的伤害</t>
-  </si>
-  <si>
-    <t>cd</t>
-  </si>
-  <si>
-    <t>武器发射需要的时间</t>
-  </si>
-  <si>
-    <t>unlock</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器</t>
-  </si>
-  <si>
-    <t>res_1</t>
-  </si>
-  <si>
-    <t>升级该武器需要的资源</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为res_x。如res_2，res_3就表示第二种，第三种资源。资源为res表的id</t>
-  </si>
-  <si>
-    <t>cost_1</t>
-  </si>
-  <si>
-    <t>升到该等级需要的资源数量</t>
-  </si>
-  <si>
-    <t>支持不做修改就能扩展，格式均为cost_x。如cost_2，cost_3就表示第二种，第三种资源消耗量。与res_x一一对应</t>
-  </si>
-  <si>
-    <t>para1</t>
-  </si>
-  <si>
-    <t>武器的额外参数。具体每个武器再定义，一般可参考des</t>
-  </si>
-  <si>
-    <t>mon</t>
+    <t>dmgMultiple</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>armourType</t>
+  </si>
+  <si>
+    <t>res</t>
+  </si>
+  <si>
+    <t>size</t>
   </si>
   <si>
     <t>敌方飞行器id</t>
@@ -196,214 +59,43 @@
     <t>飞行器描述</t>
   </si>
   <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的</t>
-  </si>
-  <si>
-    <t>dmgMultiple</t>
+    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的,格式为｛name|数量，name|数量...}</t>
   </si>
   <si>
     <t>武器的伤害乘该值，这样计算完后的就是这个飞行器的伤害</t>
   </si>
   <si>
-    <t>health</t>
-  </si>
-  <si>
     <t>飞行器生命</t>
   </si>
   <si>
-    <t>res</t>
+    <t>护甲类型</t>
   </si>
   <si>
     <t>掉落的资源</t>
   </si>
   <si>
+    <t>大小</t>
+  </si>
+  <si>
+    <t>如上</t>
+  </si>
+  <si>
+    <t>1为能量，2为物理</t>
+  </si>
+  <si>
     <t>格式为｛id，数量，概率｝，id为res表的id，数量就是掉出来的数量，概率是被击毁时有多大概率掉落该资源</t>
   </si>
   <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>大小</t>
-  </si>
-  <si>
     <t>战场中占据的格子数</t>
   </si>
   <si>
-    <t>敌方飞行器组id</t>
-  </si>
-  <si>
-    <t>飞行器组描述</t>
-  </si>
-  <si>
-    <t>格式为{id1，id2....｝</t>
-  </si>
-  <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置</t>
-  </si>
-  <si>
-    <t>资源id</t>
-  </si>
-  <si>
-    <t>资源名</t>
-  </si>
-  <si>
-    <t>config</t>
-  </si>
-  <si>
-    <t>这个配置的名字</t>
-  </si>
-  <si>
-    <t>配置的描述</t>
-  </si>
-  <si>
-    <t>para_1</t>
-  </si>
-  <si>
-    <t>配置的参数</t>
-  </si>
-  <si>
-    <t>支持可扩展，会以para_1,para_2等方式不断扩张</t>
-  </si>
-  <si>
-    <t>hightech</t>
-  </si>
-  <si>
-    <t>这个高科技的名字</t>
-  </si>
-  <si>
-    <t>高科技的效果</t>
-  </si>
-  <si>
-    <t>timeCostBase</t>
-  </si>
-  <si>
-    <t>升级高科技需要的基础时间</t>
-  </si>
-  <si>
-    <t>timeCostMutiple</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为1.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>通过第几关后解锁</t>
-  </si>
-  <si>
-    <t>可变参数，可能有多个，具体效果参看高科技的效果des</t>
-  </si>
-  <si>
-    <t>如上</t>
-  </si>
-  <si>
-    <t>{2|0.1，2|0.2，2|0.3，2|0.4，2|0.5，2|0.6，2|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{2|0.1，5|0.2，2|0.3，5|0.4，2|0.5，5|0.6，2|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，1|0.4，2|0.5，3|0.6，1|0.7，2|0.8，6|0.9}</t>
-  </si>
-  <si>
-    <t>{4|0.1，5|0.2，4|0.3，5|0.4，4|0.5，5|0.6，4|0.7，5|0.8，7|0.9}</t>
-  </si>
-  <si>
-    <t>{1|0.1，2|0.2，3|0.3，4|0.4，5|0.5，1|0.6，2|0.7，3|0.8，8|0.9}</t>
-  </si>
-  <si>
-    <t>dmgtype</t>
-  </si>
-  <si>
-    <t>res_2</t>
-  </si>
-  <si>
-    <t>cost_2</t>
-  </si>
-  <si>
-    <t>para2</t>
-  </si>
-  <si>
-    <t>para3</t>
-  </si>
-  <si>
-    <t>伤害类型，1为能量，2为物理。</t>
-  </si>
-  <si>
-    <t>对应level表id，通关对应id的关卡后解锁该武器。不填则这行无意义</t>
-  </si>
-  <si>
-    <t>armour</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础生命，如果没了，飞船就会爆炸！然后后退。额外参数para1是生命值，dmgtype表明护甲对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>这个是飞船的基础护盾，护盾会先于护甲被扣除，同时护盾会缓慢恢复。额外参数para1是护盾值，para2是每秒恢复的比例，para3是连续多少秒不受攻击后才开始恢复，被攻击会立即停止恢复，dmgtype表明护盾对这个类型的伤害有减伤</t>
-  </si>
-  <si>
-    <t>laser</t>
-  </si>
-  <si>
-    <t>激光武器，发射一个光束攻击锁定目标，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>missile</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发。para2是导弹飞行速度</t>
-  </si>
-  <si>
-    <t>导弹武器，导弹会锁定多个敌人，锁定数量为para1定义。但敌人数量不足则只会发射敌人数量的导弹，不会多发</t>
-  </si>
-  <si>
-    <t>cannon</t>
-  </si>
-  <si>
-    <t>火炮武器，与激光一样，发射一个炮弹攻击锁定目标敌人，para1是飞行速度/S</t>
-  </si>
-  <si>
-    <t>laser_mon</t>
-  </si>
-  <si>
-    <t>missile-mon</t>
-  </si>
-  <si>
-    <t>cannon-mon</t>
-  </si>
-  <si>
-    <t>armourType</t>
-  </si>
-  <si>
-    <t>使用的武器，从equipment表中读出来，逻辑等都使用该武器表的,格式为｛name|数量，name|数量...}</t>
-  </si>
-  <si>
-    <t>护甲类型</t>
-  </si>
-  <si>
-    <t>1为能量，2为物理</t>
-  </si>
-  <si>
     <t>激光飞船</t>
   </si>
   <si>
     <t>｛laser_mon|1｝</t>
   </si>
   <si>
-    <t>{1,10,0.5}</t>
+    <t>{1,10,1}</t>
   </si>
   <si>
     <t>火炮飞船</t>
@@ -415,7 +107,7 @@
     <t>激光飞船-弱</t>
   </si>
   <si>
-    <t>{1,5,0.2}</t>
+    <t>{1,10,0.4}</t>
   </si>
   <si>
     <t>火炮飞船-弱</t>
@@ -424,136 +116,16 @@
     <t>BOSS-抵抗物理</t>
   </si>
   <si>
-    <t>｛laser_mon|2,cannon-mon|2｝</t>
-  </si>
-  <si>
-    <t>{2,1,1}</t>
+    <t>｛cannon-mon|2｝</t>
+  </si>
+  <si>
+    <t>{1,50,1}</t>
   </si>
   <si>
     <t>BOSS-抵抗能量</t>
   </si>
   <si>
-    <t>战场从上到下一共是10个格子，这里的id是mon表的id，1-10分别对应10个格子的位置，null表示此处无飞船｝</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，1，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，2，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>基础飞船组</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，1，2，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>激光飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，3，3，3，3，3，3，null，null}</t>
-  </si>
-  <si>
-    <t>火炮飞船-弱*6</t>
-  </si>
-  <si>
-    <t>｛null，null，4，4，4，4，4，4，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗物理</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，5，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-抵抗能量</t>
-  </si>
-  <si>
-    <t>｛null，null，null，null，6，null，null，null，null，null}</t>
-  </si>
-  <si>
-    <t>BOSS飞船-双BOSS</t>
-  </si>
-  <si>
-    <t>｛null，null，null，5，null，null，6，null，null，null}</t>
-  </si>
-  <si>
-    <t>铁</t>
-  </si>
-  <si>
-    <t>铝</t>
-  </si>
-  <si>
-    <t>startEquip</t>
-  </si>
-  <si>
-    <t>飞船初始具有的装备，格式为name,name，equipment表的名字。默认为1级。</t>
-  </si>
-  <si>
-    <t>armour,laser</t>
-  </si>
-  <si>
-    <t>dmgReduce</t>
-  </si>
-  <si>
-    <t>护甲类型对应时，减少的伤害</t>
-  </si>
-  <si>
-    <t>movement</t>
-  </si>
-  <si>
-    <t>飞船的移动速度，单位是秒</t>
-  </si>
-  <si>
-    <t>autoCollectReduce</t>
-  </si>
-  <si>
-    <t>自动拾取时的损耗</t>
-  </si>
-  <si>
-    <t>backRange</t>
-  </si>
-  <si>
-    <t>死亡时后退距离</t>
-  </si>
-  <si>
-    <t>hightechLimit</t>
-  </si>
-  <si>
-    <t>同时研发的高科技数量</t>
-  </si>
-  <si>
-    <t>这个神器的名字</t>
-  </si>
-  <si>
-    <t>神器的效果</t>
-  </si>
-  <si>
-    <t>升级神器需要的基础时间</t>
-  </si>
-  <si>
-    <t>每次升级后升级时间的乘数。例如1级10秒，这个值为0.2，则2级12秒，3级14秒...四舍五入取整</t>
-  </si>
-  <si>
-    <t>可变参数，具体效果参看神器的效果des</t>
-  </si>
-  <si>
-    <t>超时空炼铁炉</t>
-  </si>
-  <si>
-    <t>每para1秒在屏幕中生成一个铁块，总共含有根据过去一分钟的铁生成量*para2*等级的铁，向上取整，点击获取，10秒后消失</t>
-  </si>
-  <si>
-    <t>正电子聚焦装置</t>
-  </si>
-  <si>
-    <t>提高所有能量武器的伤害，效果为原伤害*（1+para1*等级）向上取整.</t>
-  </si>
-  <si>
-    <t>简并态装甲</t>
-  </si>
-  <si>
-    <t>armour当前值增加（1+para1*等级），向上取整。</t>
+    <t>｛laser_mon|2｝</t>
   </si>
 </sst>
 </file>
@@ -1169,18 +741,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1490,96 +1056,96 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="15.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="30.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="10.1111111111111" customWidth="1"/>
-    <col min="5" max="5" width="11.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="17.5555555555556" customWidth="1"/>
+    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="15.225" customWidth="1"/>
+    <col min="3" max="3" width="30.225" customWidth="1"/>
+    <col min="4" max="4" width="10.1083333333333" customWidth="1"/>
+    <col min="5" max="5" width="11.8916666666667" customWidth="1"/>
+    <col min="7" max="7" width="17.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>31</v>
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1587,22 +1153,22 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>0.5</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1613,22 +1179,22 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>0.5</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1639,22 +1205,22 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>126</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>0.3</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1665,22 +1231,22 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="D7">
         <v>0.3</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>127</v>
+        <v>26</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1691,22 +1257,22 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="H8">
         <v>2</v>
@@ -1717,22 +1283,22 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="E9">
-        <v>300</v>
+        <v>1500</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
       <c r="H9">
         <v>2</v>

--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -1171,7 +1171,7 @@
         <v>22</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1197,7 +1197,7 @@
         <v>22</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1275,7 +1275,7 @@
         <v>30</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1301,7 +1301,7 @@
         <v>30</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -1059,7 +1059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
@@ -1152,11 +1152,15 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">激光飞船</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">｛laser_mon|1｝</t>
+        </is>
       </c>
       <c r="D4">
         <v>0.5</v>
@@ -1167,8 +1171,10 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
-        <v>22</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,10,1}</t>
+        </is>
       </c>
       <c r="H4">
         <v>2</v>
@@ -1178,11 +1184,15 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火炮飞船</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">｛cannon-mon|1｝</t>
+        </is>
       </c>
       <c r="D5">
         <v>0.5</v>
@@ -1193,8 +1203,10 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" t="s">
-        <v>22</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,10,1}</t>
+        </is>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1204,11 +1216,15 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">激光飞船-弱</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">｛laser_mon|1｝</t>
+        </is>
       </c>
       <c r="D6">
         <v>0.3</v>
@@ -1219,8 +1235,10 @@
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>26</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,10,0.4}</t>
+        </is>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1230,11 +1248,15 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">火炮飞船-弱</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">｛cannon-mon|1｝</t>
+        </is>
       </c>
       <c r="D7">
         <v>0.3</v>
@@ -1243,10 +1265,12 @@
         <v>200</v>
       </c>
       <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
+        <v>2</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,10,0.4}</t>
+        </is>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1256,14 +1280,18 @@
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中型-抵抗物理</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">｛cannon-mon|2｝</t>
+        </is>
       </c>
       <c r="D8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>1500</v>
@@ -1271,8 +1299,10 @@
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8" t="s">
-        <v>30</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,50,1}</t>
+        </is>
       </c>
       <c r="H8">
         <v>3</v>
@@ -1282,14 +1312,18 @@
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中型-抵抗能量</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">｛laser_mon|2｝</t>
+        </is>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>1500</v>
@@ -1297,11 +1331,77 @@
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
-        <v>30</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,50,1}</t>
+        </is>
       </c>
       <c r="H9">
         <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大型-双武器-抵抗能量</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{laser_mon|2,cannon-mon|2}</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>2500</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,100,1}</t>
+        </is>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>8</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大型-双武器-抵抗物理</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{laser_mon|2,cannon-mon|2}</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>2500</v>
+      </c>
+      <c r="F11">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{1,100,1}</t>
+        </is>
+      </c>
+      <c r="H11">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\放置\space-battleship\config_excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="29868" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="mon" sheetId="4" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
@@ -89,7 +94,7 @@
     <t>战场中占据的格子数</t>
   </si>
   <si>
-    <t>激光飞船</t>
+    <t>曙光级截击舰</t>
   </si>
   <si>
     <t>｛laser_mon|1｝</t>
@@ -98,22 +103,22 @@
     <t>{1,10,1}</t>
   </si>
   <si>
-    <t>火炮飞船</t>
+    <t>裂星级突击舰</t>
   </si>
   <si>
     <t>｛cannon-mon|1｝</t>
   </si>
   <si>
-    <t>激光飞船-弱</t>
+    <t>微光级侦察艇</t>
   </si>
   <si>
     <t>{1,10,0.4}</t>
   </si>
   <si>
-    <t>火炮飞船-弱</t>
-  </si>
-  <si>
-    <t>BOSS-抵抗物理</t>
+    <t>猎隼级轻炮艇</t>
+  </si>
+  <si>
+    <t>玄武级装甲舰</t>
   </si>
   <si>
     <t>｛cannon-mon|2｝</t>
@@ -122,10 +127,55 @@
     <t>{1,50,1}</t>
   </si>
   <si>
-    <t>BOSS-抵抗能量</t>
+    <t>辉盾级能防舰</t>
   </si>
   <si>
     <t>｛laser_mon|2｝</t>
+  </si>
+  <si>
+    <t>圣辉级巡洋舰</t>
+  </si>
+  <si>
+    <t>{laser_mon|4}</t>
+  </si>
+  <si>
+    <t>{1,100,1}</t>
+  </si>
+  <si>
+    <t>钢铁级重巡舰</t>
+  </si>
+  <si>
+    <t>{cannon-mon|4}</t>
+  </si>
+  <si>
+    <t>天穹级歼星舰</t>
+  </si>
+  <si>
+    <t>{laser_mon|6}</t>
+  </si>
+  <si>
+    <t>{1,200,1}</t>
+  </si>
+  <si>
+    <t>泰坦级攻城舰</t>
+  </si>
+  <si>
+    <t>{cannon-mon|6}</t>
+  </si>
+  <si>
+    <t>太阳神级旗舰</t>
+  </si>
+  <si>
+    <t>{laser_mon|8}</t>
+  </si>
+  <si>
+    <t>{1,400,1}</t>
+  </si>
+  <si>
+    <t>深渊级战争旗舰</t>
+  </si>
+  <si>
+    <t>{cannon-mon|8}</t>
   </si>
 </sst>
 </file>
@@ -1059,15 +1109,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H15"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
-    <col min="2" max="2" width="15.225" customWidth="1"/>
-    <col min="3" max="3" width="30.225" customWidth="1"/>
-    <col min="4" max="4" width="10.1083333333333" customWidth="1"/>
-    <col min="5" max="5" width="11.8916666666667" customWidth="1"/>
-    <col min="7" max="7" width="17.5583333333333" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="30.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="10.1111111111111" customWidth="1"/>
+    <col min="5" max="5" width="11.8888888888889" customWidth="1"/>
+    <col min="7" max="7" width="17.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1152,18 +1202,14 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">激光飞船</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">｛laser_mon|1｝</t>
-        </is>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E4">
         <v>500</v>
@@ -1171,10 +1217,8 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,10,1}</t>
-        </is>
+      <c r="G4" t="s">
+        <v>22</v>
       </c>
       <c r="H4">
         <v>2</v>
@@ -1184,18 +1228,14 @@
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火炮飞船</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">｛cannon-mon|1｝</t>
-        </is>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>500</v>
@@ -1203,10 +1243,8 @@
       <c r="F5">
         <v>2</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,10,1}</t>
-        </is>
+      <c r="G5" t="s">
+        <v>22</v>
       </c>
       <c r="H5">
         <v>2</v>
@@ -1216,29 +1254,23 @@
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">激光飞船-弱</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">｛laser_mon|1｝</t>
-        </is>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E6">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,10,0.4}</t>
-        </is>
+      <c r="G6" t="s">
+        <v>26</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1248,29 +1280,23 @@
       <c r="A7">
         <v>4</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">火炮飞船-弱</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">｛cannon-mon|1｝</t>
-        </is>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
       </c>
       <c r="D7">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E7">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>2</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,10,0.4}</t>
-        </is>
+      <c r="G7" t="s">
+        <v>26</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1280,29 +1306,23 @@
       <c r="A8">
         <v>5</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中型-抵抗物理</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">｛cannon-mon|2｝</t>
-        </is>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F8">
         <v>2</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,50,1}</t>
-        </is>
+      <c r="G8" t="s">
+        <v>30</v>
       </c>
       <c r="H8">
         <v>3</v>
@@ -1312,50 +1332,40 @@
       <c r="A9">
         <v>6</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">中型-抵抗能量</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">｛laser_mon|2｝</t>
-        </is>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="F9">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,50,1}</t>
-        </is>
+      <c r="G9" t="s">
+        <v>30</v>
       </c>
       <c r="H9">
         <v>3</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>7</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大型-双武器-抵抗能量</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{laser_mon|2,cannon-mon|2}</t>
-        </is>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10">
         <v>2500</v>
@@ -1363,31 +1373,25 @@
       <c r="F10">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,100,1}</t>
-        </is>
+      <c r="G10" t="s">
+        <v>35</v>
       </c>
       <c r="H10">
         <v>4</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>8</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">大型-双武器-抵抗物理</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{laser_mon|2,cannon-mon|2}</t>
-        </is>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11">
         <v>2500</v>
@@ -1395,13 +1399,115 @@
       <c r="F11">
         <v>2</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{1,100,1}</t>
-        </is>
+      <c r="G11" t="s">
+        <v>35</v>
       </c>
       <c r="H11">
         <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>3000</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>3000</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>4000</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>45</v>
+      </c>
+      <c r="H14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>4000</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>45</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -1004,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.1111111111111" customWidth="1" style="2" min="1" max="1"/>
@@ -1056,6 +1056,26 @@
           <t>size</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>shield</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>shieldType</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>shieldRecovery</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>shieldDelay</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -1098,6 +1118,26 @@
           <t>大小</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>独立护盾容量，随关卡生命倍率；0为无盾</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>护盾抗性类型：0无、1能量、2物理</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>每秒恢复最大盾量比例，受击暂停；0不恢复</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>有效命中后等待多少游戏秒才恢复</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1140,6 +1180,26 @@
           <t>战场中占据的格子数</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -1172,6 +1232,18 @@
       <c r="H4" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -1203,6 +1275,18 @@
       </c>
       <c r="H5" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1236,6 +1320,18 @@
       <c r="H6" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -1268,6 +1364,18 @@
       <c r="H7" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -1300,6 +1408,18 @@
       <c r="H8" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1332,6 +1452,18 @@
       <c r="H9" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1364,6 +1496,18 @@
       <c r="H10" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1396,6 +1540,18 @@
       <c r="H11" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1428,6 +1584,18 @@
       <c r="H12" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1460,6 +1628,18 @@
       <c r="H13" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1492,6 +1672,18 @@
       <c r="H14" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1524,6 +1716,18 @@
       <c r="H15" s="1" t="n">
         <v>6</v>
       </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1556,6 +1760,18 @@
       <c r="H16" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1588,6 +1804,18 @@
       <c r="H17" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1620,6 +1848,18 @@
       <c r="H18" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1652,6 +1892,18 @@
       <c r="H19" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1684,6 +1936,18 @@
       <c r="H20" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1716,6 +1980,18 @@
       <c r="H21" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1748,6 +2024,18 @@
       <c r="H22" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1780,6 +2068,18 @@
       <c r="H23" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1812,6 +2112,18 @@
       <c r="H24" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1844,6 +2156,18 @@
       <c r="H25" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1876,6 +2200,18 @@
       <c r="H26" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1908,6 +2244,18 @@
       <c r="H27" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1940,6 +2288,18 @@
       <c r="H28" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1972,6 +2332,18 @@
       <c r="H29" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2004,6 +2376,18 @@
       <c r="H30" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2036,6 +2420,18 @@
       <c r="H31" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2055,7 +2451,7 @@
         <v>0.1</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>2</v>
@@ -2067,6 +2463,18 @@
       </c>
       <c r="H32" s="1" t="n">
         <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="33">
@@ -2087,7 +2495,7 @@
         <v>0.1</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>2</v>
@@ -2099,6 +2507,18 @@
       </c>
       <c r="H33" s="1" t="n">
         <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="34">
@@ -2132,6 +2552,18 @@
       <c r="H34" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2164,6 +2596,18 @@
       <c r="H35" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2196,6 +2640,18 @@
       <c r="H36" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2228,6 +2684,18 @@
       <c r="H37" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2260,6 +2728,18 @@
       <c r="H38" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2292,6 +2772,18 @@
       <c r="H39" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2324,6 +2816,18 @@
       <c r="H40" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -2356,6 +2860,18 @@
       <c r="H41" s="1" t="n">
         <v>3</v>
       </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -2388,6 +2904,18 @@
       <c r="H42" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -2420,6 +2948,18 @@
       <c r="H43" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -2452,6 +2992,18 @@
       <c r="H44" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -2484,6 +3036,18 @@
       <c r="H45" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -2516,6 +3080,18 @@
       <c r="H46" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -2548,6 +3124,18 @@
       <c r="H47" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -2580,6 +3168,18 @@
       <c r="H48" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -2612,6 +3212,18 @@
       <c r="H49" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -2644,6 +3256,18 @@
       <c r="H50" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -2676,6 +3300,18 @@
       <c r="H51" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -2708,6 +3344,18 @@
       <c r="H52" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -2740,6 +3388,18 @@
       <c r="H53" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -2772,6 +3432,18 @@
       <c r="H54" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -2804,6 +3476,18 @@
       <c r="H55" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -2836,6 +3520,18 @@
       <c r="H56" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -2868,6 +3564,18 @@
       <c r="H57" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -2887,7 +3595,7 @@
         <v>7.5</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>64000</v>
+        <v>32000</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>2</v>
@@ -2899,6 +3607,18 @@
       </c>
       <c r="H58" s="1" t="n">
         <v>4</v>
+      </c>
+      <c r="I58" t="n">
+        <v>32000</v>
+      </c>
+      <c r="J58" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="59">
@@ -2919,7 +3639,7 @@
         <v>7.5</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>50000</v>
+        <v>25000</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>2</v>
@@ -2931,6 +3651,18 @@
       </c>
       <c r="H59" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J59" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="60">
@@ -2964,6 +3696,18 @@
       <c r="H60" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -2996,6 +3740,18 @@
       <c r="H61" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -3028,6 +3784,18 @@
       <c r="H62" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -3060,6 +3828,18 @@
       <c r="H63" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -3092,6 +3872,18 @@
       <c r="H64" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -3124,6 +3916,18 @@
       <c r="H65" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -3156,6 +3960,18 @@
       <c r="H66" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -3188,6 +4004,18 @@
       <c r="H67" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -3220,6 +4048,18 @@
       <c r="H68" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -3252,6 +4092,18 @@
       <c r="H69" s="1" t="n">
         <v>4</v>
       </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -3284,6 +4136,18 @@
       <c r="H70" s="1" t="n">
         <v>2</v>
       </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -3316,6 +4180,18 @@
       <c r="H71" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -3323,7 +4199,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>编排草案-boss-physical-尺寸5</t>
+          <t>物理甲BOSS：长激光占优</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -3335,10 +4211,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>330000</v>
+        <v>440000</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
@@ -3347,6 +4223,18 @@
       </c>
       <c r="H72" s="1" t="n">
         <v>5</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3355,7 +4243,7 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>编排草案-boss-energy-尺寸5</t>
+          <t>能量盾BOSS：磁轨占优</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -3367,7 +4255,7 @@
         <v>11</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>440000</v>
+        <v>15000</v>
       </c>
       <c r="F73" s="1" t="n">
         <v>2</v>
@@ -3379,6 +4267,18 @@
       </c>
       <c r="H73" s="1" t="n">
         <v>5</v>
+      </c>
+      <c r="I73" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3387,7 +4287,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>编排草案-ultimate-physical-尺寸6</t>
+          <t>物理甲终极：长激光占优</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -3399,10 +4299,10 @@
         <v>6.6</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>850000</v>
+        <v>1250000</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
@@ -3411,6 +4311,18 @@
       </c>
       <c r="H74" s="1" t="n">
         <v>6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -3419,7 +4331,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>编排草案-ultimate-energy-尺寸6</t>
+          <t>能量盾终极：磁轨占优</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -3431,7 +4343,7 @@
         <v>6.6</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>1250000</v>
+        <v>40000</v>
       </c>
       <c r="F75" s="1" t="n">
         <v>2</v>
@@ -3443,6 +4355,18 @@
       </c>
       <c r="H75" s="1" t="n">
         <v>6</v>
+      </c>
+      <c r="I75" t="n">
+        <v>770000</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -1056,22 +1056,22 @@
           <t>size</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>shield</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>shieldType</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>shieldRecovery</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>shieldDelay</t>
         </is>
@@ -1118,22 +1118,22 @@
           <t>大小</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>独立护盾容量，随关卡生命倍率；0为无盾</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>护盾抗性类型：0无、1能量、2物理</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>每秒恢复最大盾量比例，受击暂停；0不恢复</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>有效命中后等待多少游戏秒才恢复</t>
         </is>
@@ -1180,22 +1180,22 @@
           <t>战场中占据的格子数</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -1232,16 +1232,16 @@
       <c r="H4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="I4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1276,16 +1276,16 @@
       <c r="H5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1320,16 +1320,16 @@
       <c r="H6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1364,16 +1364,16 @@
       <c r="H7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1408,16 +1408,16 @@
       <c r="H8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="I8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1452,16 +1452,16 @@
       <c r="H9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1496,16 +1496,16 @@
       <c r="H10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1540,16 +1540,16 @@
       <c r="H11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="I11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1584,16 +1584,16 @@
       <c r="H12" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1628,16 +1628,16 @@
       <c r="H13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1672,16 +1672,16 @@
       <c r="H14" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="I14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1716,16 +1716,16 @@
       <c r="H15" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="I15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1760,16 +1760,16 @@
       <c r="H16" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="I16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1804,16 +1804,16 @@
       <c r="H17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="I17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1848,16 +1848,16 @@
       <c r="H18" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="I18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1892,16 +1892,16 @@
       <c r="H19" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="I19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1936,16 +1936,16 @@
       <c r="H20" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="I20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1980,16 +1980,16 @@
       <c r="H21" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="I21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2024,16 +2024,16 @@
       <c r="H22" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="I22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2068,16 +2068,16 @@
       <c r="H23" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="I23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2112,16 +2112,16 @@
       <c r="H24" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="I24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2156,16 +2156,16 @@
       <c r="H25" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="I25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2200,16 +2200,16 @@
       <c r="H26" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="I26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2244,16 +2244,16 @@
       <c r="H27" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="I27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2288,16 +2288,16 @@
       <c r="H28" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="I28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2332,16 +2332,16 @@
       <c r="H29" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="I29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2376,16 +2376,16 @@
       <c r="H30" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="I30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2420,16 +2420,16 @@
       <c r="H31" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="I31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2464,16 +2464,16 @@
       <c r="H32" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
+      <c r="J32" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2508,16 +2508,16 @@
       <c r="H33" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33" s="1" t="n">
         <v>8000</v>
       </c>
-      <c r="J33" t="n">
-        <v>2</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="J33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K33" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2552,16 +2552,16 @@
       <c r="H34" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
+      <c r="I34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2596,16 +2596,16 @@
       <c r="H35" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
+      <c r="I35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2640,16 +2640,16 @@
       <c r="H36" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
+      <c r="I36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2684,16 +2684,16 @@
       <c r="H37" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
+      <c r="I37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2728,16 +2728,16 @@
       <c r="H38" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="I38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2772,16 +2772,16 @@
       <c r="H39" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
+      <c r="I39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2816,16 +2816,16 @@
       <c r="H40" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
+      <c r="I40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2860,16 +2860,16 @@
       <c r="H41" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="I41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2904,16 +2904,16 @@
       <c r="H42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
+      <c r="I42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2948,16 +2948,16 @@
       <c r="H43" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
+      <c r="I43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2992,16 +2992,16 @@
       <c r="H44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
+      <c r="I44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3036,16 +3036,16 @@
       <c r="H45" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
+      <c r="I45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3080,16 +3080,16 @@
       <c r="H46" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
+      <c r="I46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3124,16 +3124,16 @@
       <c r="H47" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
+      <c r="I47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3168,16 +3168,16 @@
       <c r="H48" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
+      <c r="I48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3212,16 +3212,16 @@
       <c r="H49" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
+      <c r="I49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3256,16 +3256,16 @@
       <c r="H50" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
+      <c r="I50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3300,16 +3300,16 @@
       <c r="H51" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
+      <c r="I51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3344,16 +3344,16 @@
       <c r="H52" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
+      <c r="I52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3388,16 +3388,16 @@
       <c r="H53" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
+      <c r="I53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3432,16 +3432,16 @@
       <c r="H54" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
+      <c r="I54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
       <c r="H55" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
+      <c r="I55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3520,16 +3520,16 @@
       <c r="H56" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
+      <c r="I56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3564,16 +3564,16 @@
       <c r="H57" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
+      <c r="I57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3595,7 +3595,7 @@
         <v>7.5</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>32000</v>
+        <v>22800</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>2</v>
@@ -3608,16 +3608,16 @@
       <c r="H58" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I58" t="n">
-        <v>32000</v>
-      </c>
-      <c r="J58" t="n">
-        <v>2</v>
-      </c>
-      <c r="K58" t="n">
+      <c r="I58" s="1" t="n">
+        <v>22800</v>
+      </c>
+      <c r="J58" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K58" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -3639,7 +3639,7 @@
         <v>7.5</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>25000</v>
+        <v>17800</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>2</v>
@@ -3652,16 +3652,16 @@
       <c r="H59" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I59" t="n">
-        <v>25000</v>
-      </c>
-      <c r="J59" t="n">
-        <v>2</v>
-      </c>
-      <c r="K59" t="n">
+      <c r="I59" s="1" t="n">
+        <v>17800</v>
+      </c>
+      <c r="J59" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59" s="1" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
         <v>0.1</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>2</v>
@@ -3696,16 +3696,16 @@
       <c r="H60" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
+      <c r="I60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>7.1</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>10000</v>
+        <v>21000</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>2</v>
@@ -3740,16 +3740,16 @@
       <c r="H61" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
+      <c r="I61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3768,10 +3768,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>7000</v>
+        <v>11100</v>
       </c>
       <c r="F62" s="1" t="n">
         <v>1</v>
@@ -3784,16 +3784,16 @@
       <c r="H62" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
+      <c r="I62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3812,13 +3812,13 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>7.2</v>
+        <v>0.12</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>6000</v>
+        <v>16100</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
@@ -3828,16 +3828,16 @@
       <c r="H63" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
+      <c r="I63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3856,10 +3856,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>0.1</v>
+        <v>12.1</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>17000</v>
+        <v>21100</v>
       </c>
       <c r="F64" s="1" t="n">
         <v>2</v>
@@ -3872,16 +3872,16 @@
       <c r="H64" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
+      <c r="I64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3900,13 +3900,13 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>6.1</v>
+        <v>5.48</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>17000</v>
+        <v>11080</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
@@ -3916,16 +3916,16 @@
       <c r="H65" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
+      <c r="I65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3944,10 +3944,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>17000</v>
+        <v>16200</v>
       </c>
       <c r="F66" s="1" t="n">
         <v>2</v>
@@ -3960,16 +3960,16 @@
       <c r="H66" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
+      <c r="I66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3988,13 +3988,13 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>7.3</v>
+        <v>11.9</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>7500</v>
+        <v>21200</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
@@ -4004,16 +4004,16 @@
       <c r="H67" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
+      <c r="I67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4032,13 +4032,13 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>8.9</v>
+        <v>5.6</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>9000</v>
+        <v>11060</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
@@ -4048,16 +4048,16 @@
       <c r="H68" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
+      <c r="I68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4076,10 +4076,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>18000</v>
+        <v>16300</v>
       </c>
       <c r="F69" s="1" t="n">
         <v>2</v>
@@ -4092,16 +4092,16 @@
       <c r="H69" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I69" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
+      <c r="I69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>7.3</v>
+        <v>12.05</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>7600</v>
+        <v>21300</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
@@ -4136,16 +4136,16 @@
       <c r="H70" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
+      <c r="I70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4164,13 +4164,13 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>9.800000000000001</v>
+        <v>5.52</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>9000</v>
+        <v>11040</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
@@ -4180,16 +4180,16 @@
       <c r="H71" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
+      <c r="I71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>440000</v>
+        <v>315000</v>
       </c>
       <c r="F72" s="1" t="n">
         <v>2</v>
@@ -4224,16 +4224,16 @@
       <c r="H72" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
+      <c r="I72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4268,16 +4268,16 @@
       <c r="H73" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73" s="1" t="n">
         <v>300000</v>
       </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
+      <c r="J73" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
         <v>6.6</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>1250000</v>
+        <v>895000</v>
       </c>
       <c r="F74" s="1" t="n">
         <v>2</v>
@@ -4312,16 +4312,16 @@
       <c r="H74" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I74" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
+      <c r="I74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4356,16 +4356,16 @@
       <c r="H75" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75" s="1" t="n">
         <v>770000</v>
       </c>
-      <c r="J75" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
+      <c r="J75" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/space-battleship/config_excel/mon.xlsx
+++ b/space-battleship/config_excel/mon.xlsx
@@ -1004,7 +1004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L75"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.888888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.1111111111111" customWidth="1" style="2" min="1" max="1"/>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" s="2">
       <c r="A16" s="1" t="n">
         <v>1001</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" s="2">
       <c r="A17" s="1" t="n">
         <v>1002</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" s="2">
       <c r="A18" s="1" t="n">
         <v>1003</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" s="2">
       <c r="A19" s="1" t="n">
         <v>1004</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" s="2">
       <c r="A20" s="1" t="n">
         <v>1005</v>
       </c>
@@ -1949,7 +1949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" s="2">
       <c r="A21" s="1" t="n">
         <v>1006</v>
       </c>
@@ -1993,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" s="2">
       <c r="A22" s="1" t="n">
         <v>1007</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" s="2">
       <c r="A23" s="1" t="n">
         <v>1008</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" s="2">
       <c r="A24" s="1" t="n">
         <v>1009</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" s="2">
       <c r="A25" s="1" t="n">
         <v>1010</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" s="2">
       <c r="A26" s="1" t="n">
         <v>1011</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" s="2">
       <c r="A27" s="1" t="n">
         <v>1012</v>
       </c>
@@ -2257,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" s="2">
       <c r="A28" s="1" t="n">
         <v>1013</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" s="2">
       <c r="A29" s="1" t="n">
         <v>1014</v>
       </c>
@@ -2345,7 +2345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" s="2">
       <c r="A30" s="1" t="n">
         <v>1015</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" s="2">
       <c r="A31" s="1" t="n">
         <v>1016</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" s="2">
       <c r="A32" s="1" t="n">
         <v>1017</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" s="2">
       <c r="A33" s="1" t="n">
         <v>1018</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" s="2">
       <c r="A34" s="1" t="n">
         <v>1019</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" s="2">
       <c r="A35" s="1" t="n">
         <v>1020</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" s="2">
       <c r="A36" s="1" t="n">
         <v>1025</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" s="2">
       <c r="A37" s="1" t="n">
         <v>1026</v>
       </c>
@@ -2697,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" s="2">
       <c r="A38" s="1" t="n">
         <v>1031</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" s="2">
       <c r="A39" s="1" t="n">
         <v>1032</v>
       </c>
@@ -2785,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" s="2">
       <c r="A40" s="1" t="n">
         <v>1037</v>
       </c>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" s="2">
       <c r="A41" s="1" t="n">
         <v>1038</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" s="2">
       <c r="A42" s="1" t="n">
         <v>1043</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" s="2">
       <c r="A43" s="1" t="n">
         <v>1044</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" s="2">
       <c r="A44" s="1" t="n">
         <v>1045</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" s="2">
       <c r="A45" s="1" t="n">
         <v>1046</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" s="2">
       <c r="A46" s="1" t="n">
         <v>1047</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" s="2">
       <c r="A47" s="1" t="n">
         <v>1048</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" s="2">
       <c r="A48" s="1" t="n">
         <v>1049</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" s="2">
       <c r="A49" s="1" t="n">
         <v>1050</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" s="2">
       <c r="A50" s="1" t="n">
         <v>1051</v>
       </c>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" s="2">
       <c r="A51" s="1" t="n">
         <v>1052</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" s="2">
       <c r="A52" s="1" t="n">
         <v>1053</v>
       </c>
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" s="2">
       <c r="A53" s="1" t="n">
         <v>1054</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" s="2">
       <c r="A54" s="1" t="n">
         <v>1055</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" s="2">
       <c r="A55" s="1" t="n">
         <v>1056</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" s="2">
       <c r="A56" s="1" t="n">
         <v>1057</v>
       </c>
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" s="2">
       <c r="A57" s="1" t="n">
         <v>1058</v>
       </c>
@@ -3577,7 +3577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" s="2">
       <c r="A58" s="1" t="n">
         <v>1062</v>
       </c>
@@ -3621,7 +3621,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" s="2">
       <c r="A59" s="1" t="n">
         <v>1063</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" s="2">
       <c r="A60" s="1" t="n">
         <v>1067</v>
       </c>
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" s="2">
       <c r="A61" s="1" t="n">
         <v>1068</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" s="2">
       <c r="A62" s="1" t="n">
         <v>1069</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" s="2">
       <c r="A63" s="1" t="n">
         <v>1072</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" s="2">
       <c r="A64" s="1" t="n">
         <v>1073</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" s="2">
       <c r="A65" s="1" t="n">
         <v>1074</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" s="2">
       <c r="A66" s="1" t="n">
         <v>1077</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" s="2">
       <c r="A67" s="1" t="n">
         <v>1078</v>
       </c>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" s="2">
       <c r="A68" s="1" t="n">
         <v>1079</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" s="2">
       <c r="A69" s="1" t="n">
         <v>1082</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" s="2">
       <c r="A70" s="1" t="n">
         <v>1083</v>
       </c>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" s="2">
       <c r="A71" s="1" t="n">
         <v>1084</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" s="2">
       <c r="A72" s="1" t="n">
         <v>1087</v>
       </c>
@@ -4237,7 +4237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" s="2">
       <c r="A73" s="1" t="n">
         <v>1088</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" s="2">
       <c r="A74" s="1" t="n">
         <v>1089</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" s="2">
       <c r="A75" s="1" t="n">
         <v>1090</v>
       </c>
@@ -4366,6 +4366,2646 @@
         <v>0</v>
       </c>
       <c r="L75" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-laser-尺寸2 · 物理攻击变体（源模板1001）</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-laser-尺寸1 · 物理攻击变体（源模板1002）</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-laser-尺寸1 · 物理攻击变体（源模板1003）</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-laser-尺寸2 · 物理攻击变体（源模板1004）</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-laser-尺寸2 · 物理攻击变体（源模板1005）</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-laser-尺寸1 · 物理攻击变体（源模板1006）</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸1 · 物理攻击变体（源模板1007）</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸2 · 物理攻击变体（源模板1008）</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸1 · 物理攻击变体（源模板1009）</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸2 · 物理攻击变体（源模板1010）</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸1 · 物理攻击变体（源模板1011）</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸2 · 物理攻击变体（源模板1012）</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸1 · 物理攻击变体（源模板1013）</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸2 · 物理攻击变体（源模板1014）</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-missile-尺寸1 · 物理攻击变体（源模板1015）</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-cannon-尺寸3 · 物理攻击变体（源模板1016）</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>80000</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-longLaser-尺寸3 · 物理攻击变体（源模板1017）</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I92" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J92" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K92" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L92" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-longLaser-尺寸3 · 物理攻击变体（源模板1018）</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I93" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="J93" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L93" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral1-尺寸2 · 物理攻击变体（源模板1019）</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H94" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral1-尺寸1 · 物理攻击变体（源模板1020）</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral2-尺寸2 · 物理攻击变体（源模板1025）</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral2-尺寸1 · 物理攻击变体（源模板1026）</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral3-尺寸2 · 物理攻击变体（源模板1031）</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral3-尺寸1 · 物理攻击变体（源模板1032）</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>2037</v>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral4-尺寸2 · 物理攻击变体（源模板1037）</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>9000</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>2038</v>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-normal-neutral4-尺寸1 · 物理攻击变体（源模板1038）</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>22000</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H101" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>2043</v>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-laser-尺寸2 · 物理攻击变体（源模板1043）</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>2044</v>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-laser-尺寸1 · 物理攻击变体（源模板1044）</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>2045</v>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-laser-尺寸4 · 物理攻击变体（源模板1045）</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>2046</v>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-laser-尺寸2 · 物理攻击变体（源模板1046）</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>14000</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>2047</v>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-laser-尺寸1 · 物理攻击变体（源模板1047）</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>2048</v>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸1 · 物理攻击变体（源模板1048）</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>2049</v>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸2 · 物理攻击变体（源模板1049）</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>2050</v>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸1 · 物理攻击变体（源模板1050）</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>2051</v>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸4 · 物理攻击变体（源模板1051）</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>2052</v>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸1 · 物理攻击变体（源模板1052）</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H111" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>2053</v>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸2 · 物理攻击变体（源模板1053）</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H112" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>2054</v>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸1 · 物理攻击变体（源模板1054）</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H113" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>2055</v>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸2 · 物理攻击变体（源模板1055）</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>2056</v>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-missile-尺寸1 · 物理攻击变体（源模板1056）</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>2057</v>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-cannon-尺寸2 · 物理攻击变体（源模板1057）</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>73000</v>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>2058</v>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-cannon-尺寸1 · 物理攻击变体（源模板1058）</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="E117" s="1" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>2062</v>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-longLaser-尺寸2 · 物理攻击变体（源模板1062）</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>22800</v>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I118" s="1" t="n">
+        <v>22800</v>
+      </c>
+      <c r="J118" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K118" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L118" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>2063</v>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-longLaser-尺寸1 · 物理攻击变体（源模板1063）</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>17800</v>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" s="1" t="n">
+        <v>17800</v>
+      </c>
+      <c r="J119" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K119" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L119" s="1" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>2067</v>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral1-尺寸2 · 物理攻击变体（源模板1067）</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>2068</v>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral1-尺寸1 · 物理攻击变体（源模板1068）</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>2069</v>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral1-尺寸4 · 物理攻击变体（源模板1069）</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>11100</v>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>2072</v>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral2-尺寸2 · 物理攻击变体（源模板1072）</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>16100</v>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>2073</v>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral2-尺寸1 · 物理攻击变体（源模板1073）</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>21100</v>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>2074</v>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral2-尺寸4 · 物理攻击变体（源模板1074）</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>11080</v>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H125" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>2077</v>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral3-尺寸2 · 物理攻击变体（源模板1077）</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>16200</v>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>2078</v>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral3-尺寸1 · 物理攻击变体（源模板1078）</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>21200</v>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>2079</v>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral3-尺寸4 · 物理攻击变体（源模板1079）</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>11060</v>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H128" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>2082</v>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral4-尺寸2 · 物理攻击变体（源模板1082）</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>16300</v>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>2083</v>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral4-尺寸1 · 物理攻击变体（源模板1083）</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>21300</v>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>2084</v>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>编排草案-elite-neutral4-尺寸4 · 物理攻击变体（源模板1084）</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E131" s="1" t="n">
+        <v>11040</v>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>2087</v>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>物理甲BOSS：长激光占优 · 物理攻击变体（源模板1087）</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E132" s="1" t="n">
+        <v>315000</v>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>2088</v>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>能量盾BOSS：磁轨占优 · 物理攻击变体（源模板1088）</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E133" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H133" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="I133" s="1" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J133" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K133" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>2089</v>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>物理甲终极：长激光占优 · 物理攻击变体（源模板1089）</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>895000</v>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H134" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>2090</v>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>能量盾终极：磁轨占优 · 物理攻击变体（源模板1090）</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>{cannon-mon|1}</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G135" s="1" t="inlineStr">
+        <is>
+          <t>{1,0,0}</t>
+        </is>
+      </c>
+      <c r="H135" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="I135" s="1" t="n">
+        <v>770000</v>
+      </c>
+      <c r="J135" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K135" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="1" t="n">
         <v>0</v>
       </c>
     </row>
